--- a/Работы и операции по разработке изделий согласно ГОСТ_v.00 r.04 + новые задачи.xlsx
+++ b/Работы и операции по разработке изделий согласно ГОСТ_v.00 r.04 + новые задачи.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="914">
   <si>
     <t>Сводная таблица операций согласно ГОСТ ЕСКД, ЕСПД, СРПП и стандартов по программной инженерии</t>
   </si>
@@ -2768,9 +2768,6 @@
     <t>Сборка</t>
   </si>
   <si>
-    <t>Слесарь-сборщик</t>
-  </si>
-  <si>
     <t>1 85 151, коды 8800-8882</t>
   </si>
   <si>
@@ -3012,9 +3009,6 @@
   </si>
   <si>
     <t>16.3</t>
-  </si>
-  <si>
-    <t>16.4</t>
   </si>
   <si>
     <t>Научный сотрудник, инженер-исследователь, инженер-разработчик, инженер-конструктор, инженер-программист (инженер-программист-системотехник), инженер-электроник, инженер-системотехник, инженер-схемотехник</t>
@@ -3325,9 +3319,6 @@
     <t>Управление проектом</t>
   </si>
   <si>
-    <t>Разработка эксплуатационных документов (паспорта, формуляра, этикетки, РЭ)</t>
-  </si>
-  <si>
     <t>Инженер-конструктор, инженер-программист, инженер по НТД</t>
   </si>
   <si>
@@ -3494,9 +3485,6 @@
   </si>
   <si>
     <t>Выполнение лужения</t>
-  </si>
-  <si>
-    <t>Выполнение регулировки, настройки, юстировки</t>
   </si>
   <si>
     <t>Выполнение разделки провода, кабеля, жилы</t>
@@ -3695,9 +3683,6 @@
     <t>17.14</t>
   </si>
   <si>
-    <t xml:space="preserve"> Планирование проекта (соотносится с 1.4* в части НИР, НИОКР, ОКР)</t>
-  </si>
-  <si>
     <t>Выполнение обмена информацией и коммуникаций в рамках проекта</t>
   </si>
   <si>
@@ -3804,6 +3789,72 @@
   </si>
   <si>
     <t>Выполнение определения, оценки и анализа метрологических характеристик готовых приборов или измерительных (генерирующих) каналов в рамках процедур калибровки или поверки</t>
+  </si>
+  <si>
+    <t>Разработка эксплуатационных документов (паспорта, формуляра, этикетки, РЭ, методик поверки/калибровки)</t>
+  </si>
+  <si>
+    <t>Выполнение регулировки, настройки, юстировки электроники</t>
+  </si>
+  <si>
+    <t>13.8</t>
+  </si>
+  <si>
+    <t>Выполнение регулировки, настройки, юстировки механики или электромеханики</t>
+  </si>
+  <si>
+    <t>Сборка и монтаж механическая</t>
+  </si>
+  <si>
+    <t>Монтажник РЭА, слесарь-сборщик, регулировщик</t>
+  </si>
+  <si>
+    <t>Монтажник РЭА, регулировщик РЭАиП</t>
+  </si>
+  <si>
+    <t>Слесарь-сборщик, монтажник РЭА</t>
+  </si>
+  <si>
+    <t>14.7.1</t>
+  </si>
+  <si>
+    <t>Выполнение подготовительных работ с изделием (СЕ) непосредственно перед проведением испытаний (кроме регулировок, настроек, калибровки/поверки)</t>
+  </si>
+  <si>
+    <t>14.7.2</t>
+  </si>
+  <si>
+    <t>Непосредственное проведение испытаний (функциональных, производительности, старения и т.д.)</t>
+  </si>
+  <si>
+    <t>14.7.3</t>
+  </si>
+  <si>
+    <t>Подготовка к испытаниям (размещение/установка объекта испытаний на испытательном оборудовании/стенде, сборка испытательной установки и схемы, подготовка стендового и измерительного оборудования, выполнение мер безопасности, инструктаж участников испытания, подготовка документации)</t>
+  </si>
+  <si>
+    <t>Завершение испытаний и протоколирование результатов, их анализ, формирование актов (протоколов)</t>
+  </si>
+  <si>
+    <t>Непосредственное выполнение испытатний  (согласно ПМ испытаний) и заполнение протоколов (чек-листов) по ним</t>
+  </si>
+  <si>
+    <t>Выполнение работ по демонтажу (снятию) испытуемого изделия (СЕ) после проведения испытаний со стенда и разборка испытательной установки/схемы, формирование актов (протоколов) с выводами (заключениями)</t>
+  </si>
+  <si>
+    <t>Планирование проекта (соотносится с 1.4* в части НИР, НИОКР, ОКР)</t>
+  </si>
+  <si>
+    <t>16.5</t>
+  </si>
+  <si>
+    <t>Найм и работа с новым персоналом</t>
+  </si>
+  <si>
+    <t>16.6</t>
+  </si>
+  <si>
+    <t>Закупка и/или заказ материалов</t>
   </si>
 </sst>
 </file>
@@ -3996,7 +4047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4056,6 +4107,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4086,6 +4152,9 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4098,22 +4167,19 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4407,14 +4473,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="2" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -4431,12 +4497,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
     </row>
     <row r="4" spans="1:6" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -4579,12 +4645,12 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="34"/>
     </row>
     <row r="15" spans="1:6" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -4671,12 +4737,12 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="34"/>
     </row>
     <row r="22" spans="1:4" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -4735,12 +4801,12 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="34"/>
     </row>
     <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -4911,12 +4977,12 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="29"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="34"/>
     </row>
     <row r="40" spans="1:4" ht="66" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -5015,12 +5081,12 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="29"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="34"/>
     </row>
     <row r="48" spans="1:4" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
@@ -5205,12 +5271,12 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="29"/>
+      <c r="B61" s="33"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="34"/>
     </row>
     <row r="62" spans="1:4" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
@@ -5381,12 +5447,12 @@
       </c>
     </row>
     <row r="74" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="27" t="s">
+      <c r="A74" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B74" s="28"/>
-      <c r="C74" s="28"/>
-      <c r="D74" s="29"/>
+      <c r="B74" s="33"/>
+      <c r="C74" s="33"/>
+      <c r="D74" s="34"/>
     </row>
     <row r="75" spans="1:4" ht="33" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
@@ -5627,12 +5693,12 @@
       </c>
     </row>
     <row r="92" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="27" t="s">
+      <c r="A92" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="B92" s="28"/>
-      <c r="C92" s="28"/>
-      <c r="D92" s="29"/>
+      <c r="B92" s="33"/>
+      <c r="C92" s="33"/>
+      <c r="D92" s="34"/>
     </row>
     <row r="93" spans="1:4" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
@@ -5705,12 +5771,12 @@
       </c>
     </row>
     <row r="98" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="27" t="s">
+      <c r="A98" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="B98" s="28"/>
-      <c r="C98" s="28"/>
-      <c r="D98" s="29"/>
+      <c r="B98" s="33"/>
+      <c r="C98" s="33"/>
+      <c r="D98" s="34"/>
     </row>
     <row r="99" spans="1:4" ht="33" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
@@ -5909,12 +5975,12 @@
       </c>
     </row>
     <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="27" t="s">
+      <c r="A113" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="B113" s="28"/>
-      <c r="C113" s="28"/>
-      <c r="D113" s="29"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="33"/>
+      <c r="D113" s="34"/>
     </row>
     <row r="114" spans="1:4" ht="33" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
@@ -6001,12 +6067,12 @@
       </c>
     </row>
     <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="27" t="s">
+      <c r="A120" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="B120" s="28"/>
-      <c r="C120" s="28"/>
-      <c r="D120" s="29"/>
+      <c r="B120" s="33"/>
+      <c r="C120" s="33"/>
+      <c r="D120" s="34"/>
     </row>
     <row r="121" spans="1:4" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
@@ -6205,10 +6271,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I147"/>
+  <dimension ref="A2:I153"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="17" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" style="17" customWidth="1"/>
     <col min="2" max="2" width="57.7109375" style="18" customWidth="1"/>
     <col min="3" max="3" width="15" style="18" customWidth="1"/>
     <col min="4" max="4" width="14.140625" style="18" customWidth="1"/>
@@ -6220,94 +6286,94 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>824</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
+      <c r="A2" s="49" t="s">
+        <v>820</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="46" t="s">
         <v>470</v>
       </c>
-      <c r="B3" s="40" t="s">
-        <v>661</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>820</v>
-      </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40" t="s">
+      <c r="B3" s="45" t="s">
+        <v>659</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>816</v>
+      </c>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45" t="s">
+        <v>815</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>471</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>472</v>
+      </c>
+      <c r="I3" s="47" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="46"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>818</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="G3" s="43" t="s">
-        <v>471</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>472</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="41"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="11" t="s">
-        <v>821</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>822</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>823</v>
-      </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>655</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
+      <c r="A5" s="48" t="s">
+        <v>653</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
     </row>
     <row r="6" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>339</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
       <c r="E6" s="21"/>
       <c r="F6" s="22" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>474</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
@@ -6315,22 +6381,22 @@
         <v>340</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="15"/>
       <c r="F7" s="14" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>474</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
@@ -6338,22 +6404,22 @@
         <v>341</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="15"/>
       <c r="F8" s="14" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6361,22 +6427,22 @@
         <v>342</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="15"/>
       <c r="F9" s="14" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6384,22 +6450,22 @@
         <v>343</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="15"/>
       <c r="F10" s="14" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6407,22 +6473,22 @@
         <v>344</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="15"/>
       <c r="F11" s="14" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>474</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
@@ -6430,7 +6496,7 @@
         <v>345</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -6439,13 +6505,13 @@
         <v>476</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>477</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
@@ -6453,22 +6519,22 @@
         <v>346</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="15"/>
       <c r="F13" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>477</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
@@ -6476,71 +6542,71 @@
         <v>347</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="15"/>
       <c r="F14" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G14" s="16" t="s">
+        <v>703</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>704</v>
+      </c>
+      <c r="I14" s="16" t="s">
         <v>705</v>
       </c>
-      <c r="H14" s="16" t="s">
-        <v>706</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>707</v>
-      </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="42" t="s">
-        <v>654</v>
-      </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
+      <c r="A15" s="48" t="s">
+        <v>652</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="48" t="s">
         <v>478</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
     </row>
     <row r="17" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>349</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="15"/>
       <c r="F17" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G17" s="33" t="s">
         <v>637</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>635</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>480</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6548,20 +6614,20 @@
         <v>350</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="15"/>
       <c r="F18" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G18" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G18" s="38"/>
       <c r="H18" s="16" t="s">
         <v>480</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6569,20 +6635,20 @@
         <v>351</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
       <c r="E19" s="15"/>
       <c r="F19" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G19" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G19" s="38"/>
       <c r="H19" s="16" t="s">
         <v>480</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6590,20 +6656,20 @@
         <v>352</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
       <c r="E20" s="15"/>
       <c r="F20" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G20" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G20" s="38"/>
       <c r="H20" s="16" t="s">
         <v>481</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -6611,20 +6677,20 @@
         <v>353</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
       <c r="E21" s="15"/>
       <c r="F21" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G21" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G21" s="38"/>
       <c r="H21" s="16" t="s">
         <v>482</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6632,56 +6698,56 @@
         <v>354</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="15"/>
       <c r="F22" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G22" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G22" s="38"/>
       <c r="H22" s="16" t="s">
         <v>52</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
     </row>
     <row r="24" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>355</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
       <c r="E24" s="15"/>
       <c r="F24" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G24" s="33" t="s">
-        <v>638</v>
+        <v>637</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>636</v>
       </c>
       <c r="H24" s="16" t="s">
         <v>480</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6689,20 +6755,20 @@
         <v>356</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
       <c r="E25" s="15"/>
       <c r="F25" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G25" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G25" s="38"/>
       <c r="H25" s="16" t="s">
         <v>480</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6710,20 +6776,20 @@
         <v>357</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
       <c r="E26" s="15"/>
       <c r="F26" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G26" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G26" s="38"/>
       <c r="H26" s="16" t="s">
         <v>483</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6731,56 +6797,56 @@
         <v>358</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
       <c r="E27" s="15"/>
       <c r="F27" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G27" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G27" s="38"/>
       <c r="H27" s="16" t="s">
         <v>65</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="39" t="s">
         <v>484</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>359</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
       <c r="E29" s="15"/>
       <c r="F29" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>485</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6788,22 +6854,22 @@
         <v>360</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
       <c r="E30" s="15"/>
       <c r="F30" s="14" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>480</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6811,22 +6877,22 @@
         <v>361</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
       <c r="E31" s="15"/>
       <c r="F31" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H31" s="16" t="s">
         <v>480</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6834,13 +6900,13 @@
         <v>362</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="15"/>
       <c r="F32" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>479</v>
@@ -6849,7 +6915,7 @@
         <v>486</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
@@ -6857,22 +6923,22 @@
         <v>363</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
       <c r="E33" s="15"/>
       <c r="F33" s="14" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>90</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
@@ -6880,22 +6946,22 @@
         <v>364</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="15"/>
       <c r="F34" s="14" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
@@ -6903,58 +6969,58 @@
         <v>365</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
       <c r="E35" s="15"/>
       <c r="F35" s="14" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H35" s="16" t="s">
         <v>96</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="39" t="s">
         <v>488</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>373</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
       <c r="E37" s="15"/>
       <c r="F37" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G37" s="33" t="s">
-        <v>638</v>
+        <v>637</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>636</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -6962,56 +7028,56 @@
         <v>374</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
       <c r="E38" s="15"/>
       <c r="F38" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G38" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G38" s="38"/>
       <c r="H38" s="16" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="34" t="s">
+      <c r="A39" s="39" t="s">
         <v>489</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
     </row>
     <row r="40" spans="1:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>382</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>737</v>
+        <v>892</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
       <c r="E40" s="15"/>
       <c r="F40" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G40" s="33" t="s">
-        <v>741</v>
+        <v>637</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>738</v>
       </c>
       <c r="H40" s="16" t="s">
         <v>490</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7019,20 +7085,20 @@
         <v>383</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
       <c r="E41" s="15"/>
       <c r="F41" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="G41" s="33"/>
+        <v>637</v>
+      </c>
+      <c r="G41" s="38"/>
       <c r="H41" s="16" t="s">
         <v>131</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7040,22 +7106,22 @@
         <v>384</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
       <c r="E42" s="15"/>
-      <c r="F42" s="38" t="s">
-        <v>648</v>
-      </c>
-      <c r="G42" s="33" t="s">
-        <v>742</v>
+      <c r="F42" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>739</v>
       </c>
       <c r="H42" s="16" t="s">
         <v>140</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7063,18 +7129,18 @@
         <v>385</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
       <c r="E43" s="15"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="33"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="38"/>
       <c r="H43" s="16" t="s">
         <v>148</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7082,18 +7148,18 @@
         <v>386</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
       <c r="E44" s="15"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="33"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="38"/>
       <c r="H44" s="16" t="s">
         <v>150</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7101,13 +7167,13 @@
         <v>387</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
       <c r="E45" s="15"/>
       <c r="F45" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G45" s="16" t="s">
         <v>487</v>
@@ -7116,7 +7182,7 @@
         <v>152</v>
       </c>
       <c r="I45" s="16" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -7124,13 +7190,13 @@
         <v>388</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
       <c r="E46" s="15"/>
       <c r="F46" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>487</v>
@@ -7139,7 +7205,7 @@
         <v>142</v>
       </c>
       <c r="I46" s="16" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7147,13 +7213,13 @@
         <v>389</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
       <c r="E47" s="15"/>
       <c r="F47" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>479</v>
@@ -7162,34 +7228,34 @@
         <v>131</v>
       </c>
       <c r="I47" s="16" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="34" t="s">
-        <v>837</v>
-      </c>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
+      <c r="A48" s="39" t="s">
+        <v>833</v>
+      </c>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="39"/>
     </row>
     <row r="49" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="B49" s="14" t="s">
-        <v>733</v>
+      <c r="B49" s="22" t="s">
+        <v>731</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
       <c r="E49" s="15"/>
       <c r="F49" s="14" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>475</v>
@@ -7198,21 +7264,21 @@
         <v>156</v>
       </c>
       <c r="I49" s="16" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="B50" s="14" t="s">
-        <v>734</v>
+      <c r="B50" s="22" t="s">
+        <v>732</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
       <c r="E50" s="15"/>
       <c r="F50" s="14" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G50" s="16" t="s">
         <v>475</v>
@@ -7221,21 +7287,21 @@
         <v>159</v>
       </c>
       <c r="I50" s="16" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="B51" s="14" t="s">
-        <v>735</v>
+      <c r="B51" s="22" t="s">
+        <v>733</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
       <c r="E51" s="15"/>
       <c r="F51" s="14" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>475</v>
@@ -7252,13 +7318,13 @@
         <v>405</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
       <c r="E52" s="15"/>
       <c r="F52" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>479</v>
@@ -7275,13 +7341,13 @@
         <v>406</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
       <c r="E53" s="15"/>
       <c r="F53" s="14" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>475</v>
@@ -7297,8 +7363,8 @@
       <c r="A54" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="B54" s="14" t="s">
-        <v>739</v>
+      <c r="B54" s="22" t="s">
+        <v>736</v>
       </c>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
@@ -7317,39 +7383,39 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="34" t="s">
+      <c r="A55" s="39" t="s">
         <v>498</v>
       </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
     </row>
     <row r="56" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>415</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
       <c r="E56" s="15"/>
       <c r="F56" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="H56" s="16" t="s">
         <v>499</v>
       </c>
       <c r="I56" s="16" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7357,13 +7423,13 @@
         <v>416</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
       <c r="E57" s="15"/>
       <c r="F57" s="14" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>500</v>
@@ -7372,7 +7438,7 @@
         <v>501</v>
       </c>
       <c r="I57" s="16" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
@@ -7380,22 +7446,22 @@
         <v>417</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
       <c r="E58" s="15"/>
       <c r="F58" s="14" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="H58" s="16" t="s">
         <v>200</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
@@ -7403,22 +7469,22 @@
         <v>418</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
       <c r="E59" s="15"/>
       <c r="F59" s="14" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="H59" s="16" t="s">
         <v>503</v>
       </c>
       <c r="I59" s="16" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -7426,22 +7492,22 @@
         <v>419</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
       <c r="E60" s="15"/>
       <c r="F60" s="14" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="H60" s="16" t="s">
         <v>503</v>
       </c>
       <c r="I60" s="16" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7449,13 +7515,13 @@
         <v>420</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
       <c r="E61" s="15"/>
       <c r="F61" s="14" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>502</v>
@@ -7464,7 +7530,7 @@
         <v>503</v>
       </c>
       <c r="I61" s="16" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
@@ -7472,13 +7538,13 @@
         <v>421</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
       <c r="E62" s="15"/>
       <c r="F62" s="14" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G62" s="16" t="s">
         <v>502</v>
@@ -7487,21 +7553,21 @@
         <v>503</v>
       </c>
       <c r="I62" s="16" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
       <c r="E63" s="15"/>
       <c r="F63" s="14" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G63" s="16"/>
       <c r="H63" s="16"/>
@@ -7509,16 +7575,16 @@
     </row>
     <row r="64" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
       <c r="E64" s="15"/>
       <c r="F64" s="14" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G64" s="16"/>
       <c r="H64" s="16"/>
@@ -7526,16 +7592,16 @@
     </row>
     <row r="65" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
       <c r="E65" s="15"/>
       <c r="F65" s="14" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G65" s="16"/>
       <c r="H65" s="16"/>
@@ -7546,13 +7612,13 @@
         <v>422</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
       <c r="E66" s="15"/>
       <c r="F66" s="14" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>487</v>
@@ -7561,28 +7627,28 @@
         <v>236</v>
       </c>
       <c r="I66" s="16" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="34" t="s">
+      <c r="A67" s="39" t="s">
         <v>504</v>
       </c>
-      <c r="B67" s="34"/>
-      <c r="C67" s="34"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="34"/>
-      <c r="I67" s="34"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="39"/>
     </row>
     <row r="68" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
         <v>432</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
@@ -7597,7 +7663,7 @@
         <v>240</v>
       </c>
       <c r="I68" s="16" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7605,7 +7671,7 @@
         <v>433</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -7620,7 +7686,7 @@
         <v>246</v>
       </c>
       <c r="I69" s="16" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7628,7 +7694,7 @@
         <v>434</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -7643,7 +7709,7 @@
         <v>144</v>
       </c>
       <c r="I70" s="16" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -7651,7 +7717,7 @@
         <v>435</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
@@ -7666,28 +7732,28 @@
         <v>250</v>
       </c>
       <c r="I71" s="16" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="34" t="s">
+      <c r="A72" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="B72" s="34"/>
-      <c r="C72" s="34"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="34"/>
-      <c r="H72" s="34"/>
-      <c r="I72" s="34"/>
+      <c r="B72" s="39"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
     </row>
     <row r="73" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>438</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -7702,7 +7768,7 @@
         <v>254</v>
       </c>
       <c r="I73" s="16" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7710,7 +7776,7 @@
         <v>439</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -7725,7 +7791,7 @@
         <v>257</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -7733,7 +7799,7 @@
         <v>440</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -7748,7 +7814,7 @@
         <v>260</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7756,7 +7822,7 @@
         <v>441</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -7771,7 +7837,7 @@
         <v>477</v>
       </c>
       <c r="I76" s="16" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -7779,7 +7845,7 @@
         <v>442</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -7794,7 +7860,7 @@
         <v>477</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7802,7 +7868,7 @@
         <v>443</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>
@@ -7817,7 +7883,7 @@
         <v>278</v>
       </c>
       <c r="I78" s="16" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -7825,7 +7891,7 @@
         <v>444</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -7840,28 +7906,28 @@
         <v>511</v>
       </c>
       <c r="I79" s="16" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="34" t="s">
+      <c r="A80" s="39" t="s">
         <v>512</v>
       </c>
-      <c r="B80" s="34"/>
-      <c r="C80" s="34"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="34"/>
-      <c r="F80" s="34"/>
-      <c r="G80" s="34"/>
-      <c r="H80" s="34"/>
-      <c r="I80" s="34"/>
+      <c r="B80" s="39"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="39"/>
+      <c r="I80" s="39"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>452</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -7884,7 +7950,7 @@
         <v>453</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -7907,7 +7973,7 @@
         <v>454</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -7930,7 +7996,7 @@
         <v>455</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -7953,7 +8019,7 @@
         <v>456</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -7976,7 +8042,7 @@
         <v>457</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -7995,24 +8061,24 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="34" t="s">
+      <c r="A87" s="39" t="s">
         <v>527</v>
       </c>
-      <c r="B87" s="34"/>
-      <c r="C87" s="34"/>
-      <c r="D87" s="34"/>
-      <c r="E87" s="34"/>
-      <c r="F87" s="34"/>
-      <c r="G87" s="34"/>
-      <c r="H87" s="34"/>
-      <c r="I87" s="34"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
     </row>
     <row r="88" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
         <v>458</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -8035,7 +8101,7 @@
         <v>459</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -8058,7 +8124,7 @@
         <v>460</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -8081,7 +8147,7 @@
         <v>461</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -8104,7 +8170,7 @@
         <v>462</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -8123,24 +8189,24 @@
       </c>
     </row>
     <row r="93" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="34" t="s">
+      <c r="A93" s="39" t="s">
         <v>542</v>
       </c>
-      <c r="B93" s="34"/>
-      <c r="C93" s="34"/>
-      <c r="D93" s="34"/>
-      <c r="E93" s="34"/>
-      <c r="F93" s="34"/>
-      <c r="G93" s="34"/>
-      <c r="H93" s="34"/>
-      <c r="I93" s="34"/>
+      <c r="B93" s="39"/>
+      <c r="C93" s="39"/>
+      <c r="D93" s="39"/>
+      <c r="E93" s="39"/>
+      <c r="F93" s="39"/>
+      <c r="G93" s="39"/>
+      <c r="H93" s="39"/>
+      <c r="I93" s="39"/>
     </row>
     <row r="94" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>794</v>
+        <v>893</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -8149,21 +8215,21 @@
         <v>543</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>537</v>
+        <v>898</v>
       </c>
       <c r="H94" s="16" t="s">
         <v>544</v>
       </c>
       <c r="I94" s="16" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -8183,10 +8249,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -8206,10 +8272,10 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -8229,10 +8295,10 @@
     </row>
     <row r="98" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -8241,21 +8307,21 @@
         <v>551</v>
       </c>
       <c r="G98" s="16" t="s">
+        <v>899</v>
+      </c>
+      <c r="H98" s="16" t="s">
         <v>552</v>
       </c>
-      <c r="H98" s="16" t="s">
+      <c r="I98" s="16" t="s">
         <v>553</v>
       </c>
-      <c r="I98" s="16" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -8264,21 +8330,21 @@
         <v>551</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>552</v>
+        <v>899</v>
       </c>
       <c r="H99" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="I99" s="16" t="s">
         <v>555</v>
       </c>
-      <c r="I99" s="16" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -8287,755 +8353,877 @@
         <v>551</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>552</v>
+        <v>899</v>
       </c>
       <c r="H100" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="I100" s="16" t="s">
         <v>557</v>
       </c>
-      <c r="I100" s="16" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="44" t="s">
-        <v>890</v>
-      </c>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="13" t="s">
-        <v>616</v>
-      </c>
-      <c r="B102" s="14" t="s">
-        <v>801</v>
-      </c>
-      <c r="C102" s="14"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="14" t="s">
-        <v>559</v>
-      </c>
-      <c r="G102" s="16" t="s">
-        <v>560</v>
-      </c>
-      <c r="H102" s="16" t="s">
-        <v>561</v>
-      </c>
-      <c r="I102" s="16" t="s">
-        <v>562</v>
-      </c>
+    </row>
+    <row r="101" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>895</v>
+      </c>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="14" t="s">
+        <v>896</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>897</v>
+      </c>
+      <c r="H101" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="I101" s="16" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="40" t="s">
+        <v>885</v>
+      </c>
+      <c r="B102" s="39"/>
+      <c r="C102" s="39"/>
+      <c r="D102" s="39"/>
+      <c r="E102" s="39"/>
+      <c r="F102" s="39"/>
+      <c r="G102" s="39"/>
+      <c r="H102" s="39"/>
+      <c r="I102" s="39"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
       <c r="E103" s="15"/>
       <c r="F103" s="14" t="s">
+        <v>558</v>
+      </c>
+      <c r="G103" s="16" t="s">
         <v>559</v>
       </c>
-      <c r="G103" s="16" t="s">
+      <c r="H103" s="16" t="s">
         <v>560</v>
       </c>
-      <c r="H103" s="16" t="s">
-        <v>563</v>
-      </c>
       <c r="I103" s="16" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C104" s="14"/>
       <c r="D104" s="14"/>
       <c r="E104" s="15"/>
       <c r="F104" s="14" t="s">
+        <v>558</v>
+      </c>
+      <c r="G104" s="16" t="s">
         <v>559</v>
       </c>
-      <c r="G104" s="16" t="s">
-        <v>560</v>
-      </c>
       <c r="H104" s="16" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="I104" s="16" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C105" s="14"/>
       <c r="D105" s="14"/>
       <c r="E105" s="15"/>
       <c r="F105" s="14" t="s">
+        <v>558</v>
+      </c>
+      <c r="G105" s="16" t="s">
         <v>559</v>
       </c>
-      <c r="G105" s="16" t="s">
-        <v>567</v>
-      </c>
       <c r="H105" s="16" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I105" s="16" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="14"/>
       <c r="E106" s="15"/>
       <c r="F106" s="14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="H106" s="16" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="I106" s="16" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>895</v>
+        <v>801</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
       <c r="E107" s="15"/>
       <c r="F107" s="14" t="s">
-        <v>893</v>
+        <v>558</v>
       </c>
       <c r="G107" s="16" t="s">
-        <v>894</v>
-      </c>
-      <c r="H107" s="16"/>
+        <v>569</v>
+      </c>
+      <c r="H107" s="16" t="s">
+        <v>570</v>
+      </c>
       <c r="I107" s="16" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>806</v>
+        <v>890</v>
       </c>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
       <c r="E108" s="15"/>
       <c r="F108" s="14" t="s">
-        <v>573</v>
+        <v>888</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>570</v>
-      </c>
-      <c r="H108" s="16" t="s">
-        <v>574</v>
-      </c>
+        <v>889</v>
+      </c>
+      <c r="H108" s="16"/>
       <c r="I108" s="16" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
       <c r="E109" s="15"/>
       <c r="F109" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="G109" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="H109" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="G109" s="16" t="s">
-        <v>570</v>
-      </c>
-      <c r="H109" s="16" t="s">
-        <v>576</v>
-      </c>
       <c r="I109" s="16" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
-        <v>624</v>
+        <v>900</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>808</v>
+        <v>905</v>
       </c>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
       <c r="E110" s="15"/>
       <c r="F110" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="H110" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="G110" s="16" t="s">
-        <v>570</v>
-      </c>
-      <c r="H110" s="16" t="s">
-        <v>578</v>
-      </c>
       <c r="I110" s="16" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
-        <v>625</v>
+        <v>902</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>809</v>
+        <v>903</v>
       </c>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
       <c r="E111" s="15"/>
       <c r="F111" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="G111" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="H111" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="G111" s="16" t="s">
-        <v>570</v>
-      </c>
-      <c r="H111" s="16" t="s">
-        <v>580</v>
-      </c>
       <c r="I111" s="16" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
-        <v>626</v>
+        <v>904</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>810</v>
+        <v>906</v>
       </c>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
       <c r="E112" s="15"/>
       <c r="F112" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="G112" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="H112" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="G112" s="16" t="s">
-        <v>570</v>
-      </c>
-      <c r="H112" s="16" t="s">
-        <v>582</v>
-      </c>
       <c r="I112" s="16" t="s">
-        <v>583</v>
+        <v>908</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
-        <v>892</v>
+        <v>622</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
       <c r="E113" s="15"/>
       <c r="F113" s="14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H113" s="16" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="I113" s="16" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="34" t="s">
-        <v>586</v>
-      </c>
-      <c r="B114" s="34"/>
-      <c r="C114" s="34"/>
-      <c r="D114" s="34"/>
-      <c r="E114" s="34"/>
-      <c r="F114" s="34"/>
-      <c r="G114" s="34"/>
-      <c r="H114" s="34"/>
-      <c r="I114" s="34"/>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="13" t="s">
+        <v>623</v>
+      </c>
+      <c r="B114" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="G114" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="H114" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="I114" s="16" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="13" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
       <c r="E115" s="15"/>
       <c r="F115" s="14" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="G115" s="16" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="H115" s="16" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="I115" s="16" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="13" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
       <c r="E116" s="15"/>
       <c r="F116" s="14" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="G116" s="16" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="H116" s="16" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="I116" s="16" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
-        <v>629</v>
+        <v>887</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
       <c r="E117" s="15"/>
       <c r="F117" s="14" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="G117" s="16" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="H117" s="16" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="I117" s="16" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="13" t="s">
-        <v>630</v>
-      </c>
-      <c r="B118" s="14" t="s">
-        <v>815</v>
-      </c>
-      <c r="C118" s="14"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="14" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="39" t="s">
+        <v>585</v>
+      </c>
+      <c r="B118" s="39"/>
+      <c r="C118" s="39"/>
+      <c r="D118" s="39"/>
+      <c r="E118" s="39"/>
+      <c r="F118" s="39"/>
+      <c r="G118" s="39"/>
+      <c r="H118" s="39"/>
+      <c r="I118" s="39"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="13" t="s">
+        <v>626</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>808</v>
+      </c>
+      <c r="C119" s="14"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="15"/>
+      <c r="F119" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="G119" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="G118" s="16" t="s">
-        <v>597</v>
-      </c>
-      <c r="H118" s="16" t="s">
-        <v>598</v>
-      </c>
-      <c r="I118" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="34" t="s">
-        <v>600</v>
-      </c>
-      <c r="B119" s="34"/>
-      <c r="C119" s="34"/>
-      <c r="D119" s="34"/>
-      <c r="E119" s="34"/>
-      <c r="F119" s="34"/>
-      <c r="G119" s="34"/>
-      <c r="H119" s="34"/>
-      <c r="I119" s="34"/>
-    </row>
-    <row r="120" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="H119" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="I119" s="16" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="13" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="C120" s="14"/>
       <c r="D120" s="14"/>
       <c r="E120" s="15"/>
       <c r="F120" s="14" t="s">
-        <v>491</v>
+        <v>590</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="H120" s="16" t="s">
-        <v>313</v>
+        <v>592</v>
       </c>
       <c r="I120" s="16" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="13" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="C121" s="14"/>
       <c r="D121" s="14"/>
       <c r="E121" s="15"/>
       <c r="F121" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="G121" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="H121" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="I121" s="16" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="13" t="s">
+        <v>629</v>
+      </c>
+      <c r="B122" s="14" t="s">
+        <v>811</v>
+      </c>
+      <c r="C122" s="14"/>
+      <c r="D122" s="14"/>
+      <c r="E122" s="15"/>
+      <c r="F122" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="G122" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="H122" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="I122" s="16" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="39" t="s">
+        <v>599</v>
+      </c>
+      <c r="B123" s="39"/>
+      <c r="C123" s="39"/>
+      <c r="D123" s="39"/>
+      <c r="E123" s="39"/>
+      <c r="F123" s="39"/>
+      <c r="G123" s="39"/>
+      <c r="H123" s="39"/>
+      <c r="I123" s="39"/>
+    </row>
+    <row r="124" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="B124" s="14" t="s">
+        <v>812</v>
+      </c>
+      <c r="C124" s="14"/>
+      <c r="D124" s="14"/>
+      <c r="E124" s="15"/>
+      <c r="F124" s="14" t="s">
         <v>491</v>
       </c>
-      <c r="G121" s="16" t="s">
+      <c r="G124" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="H124" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="I124" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="H121" s="16" t="s">
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="B125" s="14" t="s">
+        <v>813</v>
+      </c>
+      <c r="C125" s="14"/>
+      <c r="D125" s="14"/>
+      <c r="E125" s="15"/>
+      <c r="F125" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="G125" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="H125" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="I121" s="16" t="s">
+      <c r="I125" s="16" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="B126" s="22" t="s">
+        <v>814</v>
+      </c>
+      <c r="C126" s="22"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="21"/>
+      <c r="F126" s="22" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="21" t="s">
-        <v>633</v>
-      </c>
-      <c r="B122" s="22" t="s">
-        <v>818</v>
-      </c>
-      <c r="C122" s="22"/>
-      <c r="D122" s="22"/>
-      <c r="E122" s="21"/>
-      <c r="F122" s="22" t="s">
+      <c r="G126" s="22" t="s">
         <v>604</v>
       </c>
-      <c r="G122" s="22" t="s">
+      <c r="H126" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="I126" s="22" t="s">
         <v>605</v>
       </c>
-      <c r="H122" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="I122" s="22" t="s">
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>834</v>
+      </c>
+      <c r="C127" s="14"/>
+      <c r="D127" s="14"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="14" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="13" t="s">
-        <v>634</v>
-      </c>
-      <c r="B123" s="14" t="s">
-        <v>838</v>
-      </c>
-      <c r="C123" s="14"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="15"/>
-      <c r="F123" s="14" t="s">
+      <c r="G127" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="H127" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="I127" s="16" t="s">
         <v>607</v>
       </c>
-      <c r="G123" s="16" t="s">
-        <v>509</v>
-      </c>
-      <c r="H123" s="16" t="s">
-        <v>511</v>
-      </c>
-      <c r="I123" s="16" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="35" t="s">
-        <v>845</v>
-      </c>
-      <c r="B124" s="36"/>
-      <c r="C124" s="36"/>
-      <c r="D124" s="36"/>
-      <c r="E124" s="36"/>
-      <c r="F124" s="36"/>
-      <c r="G124" s="36"/>
-      <c r="H124" s="36"/>
-      <c r="I124" s="37"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="17" t="s">
-        <v>846</v>
-      </c>
-      <c r="B125" s="24" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="17" t="s">
-        <v>847</v>
-      </c>
-      <c r="B126" s="24" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="17" t="s">
-        <v>848</v>
-      </c>
-      <c r="B127" s="24" t="s">
-        <v>862</v>
-      </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="17" t="s">
-        <v>849</v>
-      </c>
-      <c r="B128" s="24" t="s">
-        <v>863</v>
-      </c>
+      <c r="A128" s="13" t="s">
+        <v>910</v>
+      </c>
+      <c r="B128" s="14" t="s">
+        <v>911</v>
+      </c>
+      <c r="C128" s="14"/>
+      <c r="D128" s="14"/>
+      <c r="E128" s="15"/>
+      <c r="F128" s="14"/>
+      <c r="G128" s="16"/>
+      <c r="H128" s="16"/>
+      <c r="I128" s="29"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="17" t="s">
-        <v>850</v>
-      </c>
-      <c r="B129" s="24" t="s">
-        <v>864</v>
-      </c>
+      <c r="A129" s="25" t="s">
+        <v>912</v>
+      </c>
+      <c r="B129" s="26" t="s">
+        <v>913</v>
+      </c>
+      <c r="C129" s="26"/>
+      <c r="D129" s="26"/>
+      <c r="E129" s="27"/>
+      <c r="F129" s="26"/>
+      <c r="G129" s="28"/>
+      <c r="H129" s="28"/>
+      <c r="I129" s="29"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="17" t="s">
-        <v>851</v>
-      </c>
-      <c r="B130" s="24" t="s">
-        <v>865</v>
-      </c>
+      <c r="A130" s="41" t="s">
+        <v>841</v>
+      </c>
+      <c r="B130" s="42"/>
+      <c r="C130" s="42"/>
+      <c r="D130" s="42"/>
+      <c r="E130" s="42"/>
+      <c r="F130" s="42"/>
+      <c r="G130" s="42"/>
+      <c r="H130" s="42"/>
+      <c r="I130" s="43"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="B131" s="24" t="s">
-        <v>866</v>
+        <v>909</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="B132" s="24" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="B133" s="24" t="s">
-        <v>868</v>
+        <v>857</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="B134" s="24" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
       <c r="B135" s="24" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="17" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="B136" s="24" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="B137" s="24" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="17" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="B138" s="24" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="30" t="s">
-        <v>874</v>
-      </c>
-      <c r="B139" s="31"/>
-      <c r="C139" s="31"/>
-      <c r="D139" s="31"/>
-      <c r="E139" s="31"/>
-      <c r="F139" s="31"/>
-      <c r="G139" s="31"/>
-      <c r="H139" s="31"/>
-      <c r="I139" s="32"/>
+      <c r="A139" s="17" t="s">
+        <v>850</v>
+      </c>
+      <c r="B139" s="24" t="s">
+        <v>863</v>
+      </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="17" t="s">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="B140" s="24" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
-        <v>876</v>
+        <v>852</v>
       </c>
       <c r="B141" s="24" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="17" t="s">
-        <v>877</v>
+        <v>853</v>
       </c>
       <c r="B142" s="24" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
+        <v>854</v>
+      </c>
+      <c r="B143" s="24" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="17" t="s">
+        <v>855</v>
+      </c>
+      <c r="B144" s="24" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="35" t="s">
+        <v>869</v>
+      </c>
+      <c r="B145" s="36"/>
+      <c r="C145" s="36"/>
+      <c r="D145" s="36"/>
+      <c r="E145" s="36"/>
+      <c r="F145" s="36"/>
+      <c r="G145" s="36"/>
+      <c r="H145" s="36"/>
+      <c r="I145" s="37"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="17" t="s">
+        <v>870</v>
+      </c>
+      <c r="B146" s="24" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="17" t="s">
+        <v>871</v>
+      </c>
+      <c r="B147" s="24" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="B148" s="24" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="B149" s="24" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="35" t="s">
         <v>878</v>
       </c>
-      <c r="B143" s="24" t="s">
+      <c r="B150" s="36"/>
+      <c r="C150" s="36"/>
+      <c r="D150" s="36"/>
+      <c r="E150" s="36"/>
+      <c r="F150" s="36"/>
+      <c r="G150" s="36"/>
+      <c r="H150" s="36"/>
+      <c r="I150" s="37"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="17" t="s">
+        <v>879</v>
+      </c>
+      <c r="B151" s="24" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="30" t="s">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="B152" s="24" t="s">
         <v>883</v>
       </c>
-      <c r="B144" s="31"/>
-      <c r="C144" s="31"/>
-      <c r="D144" s="31"/>
-      <c r="E144" s="31"/>
-      <c r="F144" s="31"/>
-      <c r="G144" s="31"/>
-      <c r="H144" s="31"/>
-      <c r="I144" s="32"/>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="17" t="s">
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="17" t="s">
+        <v>881</v>
+      </c>
+      <c r="B153" s="24" t="s">
         <v>884</v>
-      </c>
-      <c r="B145" s="24" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="17" t="s">
-        <v>885</v>
-      </c>
-      <c r="B146" s="24" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="17" t="s">
-        <v>886</v>
-      </c>
-      <c r="B147" s="24" t="s">
-        <v>889</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="A48:I48"/>
     <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="G17:G22"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="A36:I36"/>
     <mergeCell ref="G24:G27"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A139:I139"/>
-    <mergeCell ref="A144:I144"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="G17:G22"/>
+    <mergeCell ref="A145:I145"/>
+    <mergeCell ref="A150:I150"/>
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="G42:G44"/>
     <mergeCell ref="A93:I93"/>
-    <mergeCell ref="A101:I101"/>
-    <mergeCell ref="A114:I114"/>
-    <mergeCell ref="A124:I124"/>
+    <mergeCell ref="A102:I102"/>
+    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="A130:I130"/>
     <mergeCell ref="A55:I55"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A72:I72"/>
     <mergeCell ref="A80:I80"/>
     <mergeCell ref="A87:I87"/>
     <mergeCell ref="F42:F44"/>
-    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A123:I123"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Работы и операции по разработке изделий согласно ГОСТ_v.00 r.04 + новые задачи.xlsx
+++ b/Работы и операции по разработке изделий согласно ГОСТ_v.00 r.04 + новые задачи.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="912">
   <si>
     <t>Сводная таблица операций согласно ГОСТ ЕСКД, ЕСПД, СРПП и стандартов по программной инженерии</t>
   </si>
@@ -3644,15 +3644,9 @@
     <t>17.1</t>
   </si>
   <si>
-    <t>17.2</t>
-  </si>
-  <si>
     <t>17.3</t>
   </si>
   <si>
-    <t>17.4</t>
-  </si>
-  <si>
     <t>17.5</t>
   </si>
   <si>
@@ -3662,9 +3656,6 @@
     <t>17.7</t>
   </si>
   <si>
-    <t>17.8</t>
-  </si>
-  <si>
     <t>17.9</t>
   </si>
   <si>
@@ -3674,54 +3665,18 @@
     <t>17.11</t>
   </si>
   <si>
-    <t>17.12</t>
-  </si>
-  <si>
     <t>17.13</t>
   </si>
   <si>
-    <t>17.14</t>
-  </si>
-  <si>
-    <t>Выполнение обмена информацией и коммуникаций в рамках проекта</t>
-  </si>
-  <si>
     <t>Проведение совещания по проекту</t>
   </si>
   <si>
-    <t>Создание проектной документации (включая отчетную)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подготовка и предоставление отчетности по выполненным задачам и работам в проектах </t>
-  </si>
-  <si>
-    <t>Создание и сопровождение договорных документов</t>
-  </si>
-  <si>
-    <t>Координация работ по проекту</t>
-  </si>
-  <si>
-    <t>Контроль исполнения задач</t>
-  </si>
-  <si>
-    <t>Создание и сопровождение платежных документов</t>
-  </si>
-  <si>
-    <t>Создание и сопровождение документов на операции по передаче товарно-материальных ценностей (ТМЦ)</t>
-  </si>
-  <si>
     <t>Формирование сменных, дневных и рабочих заданий</t>
   </si>
   <si>
-    <t>Администрирование проекта</t>
-  </si>
-  <si>
     <t>Сопровождение работ по проекту</t>
   </si>
   <si>
-    <t>Выполнение организационных действий</t>
-  </si>
-  <si>
     <t>18. АНАЛИТИЧЕСКАЯ РАБОТА</t>
   </si>
   <si>
@@ -3734,39 +3689,21 @@
     <t>18.3</t>
   </si>
   <si>
-    <t>18.4</t>
-  </si>
-  <si>
     <t>Сбор и получение данных (включая "обратную связь")</t>
   </si>
   <si>
     <t>Анализ данных</t>
   </si>
   <si>
-    <t>Анализ результатов коммуникаций</t>
-  </si>
-  <si>
-    <t>Анализ проекта со стороны руководителя проекта (РП) или куратора проекта</t>
-  </si>
-  <si>
     <t>19. УПРАВЛЕНИЕ ВЗАИМООТНОШЕНИЯМИ С КЛИЕНТАМИ И ЗАКАЗЧИКАМИ</t>
   </si>
   <si>
-    <t>19.1</t>
-  </si>
-  <si>
     <t>19.2</t>
   </si>
   <si>
     <t>19.3</t>
   </si>
   <si>
-    <t>Работа с клиентами</t>
-  </si>
-  <si>
-    <t>Взаимодействие с заказчиком</t>
-  </si>
-  <si>
     <t>Подготовка предложений</t>
   </si>
   <si>
@@ -3855,6 +3792,63 @@
   </si>
   <si>
     <t>Закупка и/или заказ материалов</t>
+  </si>
+  <si>
+    <t>Разработка и утверждение ТЗ</t>
+  </si>
+  <si>
+    <t>Подготовка и предоставление отчетности по выполненным задачам и работам в проектах - совет по качетству</t>
+  </si>
+  <si>
+    <t>Создание и сопровождение договорных документов для внешних заказов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Создание и сопровождение платежных документов - заявки на ДС </t>
+  </si>
+  <si>
+    <t>Анализ результатов коммуникаций (включая телефонные звонки)</t>
+  </si>
+  <si>
+    <t>Координация работ по проекту - протокол совещания (Анализ проекта со стороны руководителя проекта (РП) или куратора проекта)</t>
+  </si>
+  <si>
+    <t>Командировки</t>
+  </si>
+  <si>
+    <t>Конференции</t>
+  </si>
+  <si>
+    <t>Встречи</t>
+  </si>
+  <si>
+    <t>Презентации</t>
+  </si>
+  <si>
+    <t>Выполнение Маркетингового Плана</t>
+  </si>
+  <si>
+    <t>Создание и сопровождение документов на операции по товарно-материальных ценностей (ТМЦ) - закупки и их договоры</t>
+  </si>
+  <si>
+    <t>Взаимодействие с заказчиком - ОЛ</t>
+  </si>
+  <si>
+    <t>ОПЭ</t>
+  </si>
+  <si>
+    <t>Подбор оборудования</t>
+  </si>
+  <si>
+    <t>Сертификация (СС)</t>
+  </si>
+  <si>
+    <t>Документация от ПНО Турбулентность-ДОН|Сбор документов для АО "РОСТЕСТ"|получить технологические регламенты и сведения о технологическом процессе|данные о применяемых материалах</t>
+  </si>
+  <si>
+    <t>фильтр по проектам</t>
+  </si>
+  <si>
+    <t>ДПИ</t>
   </si>
 </sst>
 </file>
@@ -4047,7 +4041,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4137,6 +4131,18 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4145,12 +4151,6 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4164,7 +4164,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4173,14 +4176,8 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6271,7 +6268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I153"/>
+  <dimension ref="A2:I158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="17" customWidth="1"/>
@@ -6286,31 +6283,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="46" t="s">
         <v>820</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="49" t="s">
         <v>470</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="48" t="s">
         <v>659</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="48" t="s">
         <v>816</v>
       </c>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45" t="s">
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48" t="s">
         <v>815</v>
       </c>
       <c r="G3" s="47" t="s">
@@ -6324,8 +6321,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="45"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="48"/>
       <c r="C4" s="11" t="s">
         <v>817</v>
       </c>
@@ -6335,23 +6332,23 @@
       <c r="E4" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="F4" s="45"/>
+      <c r="F4" s="48"/>
       <c r="G4" s="47"/>
       <c r="H4" s="47"/>
       <c r="I4" s="47"/>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="37" t="s">
         <v>653</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
     </row>
     <row r="6" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
@@ -6561,30 +6558,30 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="37" t="s">
         <v>652</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="37" t="s">
         <v>478</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
     </row>
     <row r="17" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
@@ -6715,17 +6712,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
     </row>
     <row r="24" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -6814,17 +6811,17 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="36" t="s">
         <v>484</v>
       </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
     </row>
     <row r="29" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
@@ -6988,17 +6985,17 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
+      <c r="A36" s="36" t="s">
         <v>488</v>
       </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
     </row>
     <row r="37" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
@@ -7045,24 +7042,24 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="39" t="s">
+      <c r="A39" s="36" t="s">
         <v>489</v>
       </c>
-      <c r="B39" s="39"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
     </row>
     <row r="40" spans="1:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>382</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>892</v>
+        <v>871</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -7111,7 +7108,7 @@
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
       <c r="E42" s="15"/>
-      <c r="F42" s="44" t="s">
+      <c r="F42" s="35" t="s">
         <v>646</v>
       </c>
       <c r="G42" s="38" t="s">
@@ -7134,7 +7131,7 @@
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
       <c r="E43" s="15"/>
-      <c r="F43" s="44"/>
+      <c r="F43" s="35"/>
       <c r="G43" s="38"/>
       <c r="H43" s="16" t="s">
         <v>148</v>
@@ -7153,7 +7150,7 @@
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
       <c r="E44" s="15"/>
-      <c r="F44" s="44"/>
+      <c r="F44" s="35"/>
       <c r="G44" s="38"/>
       <c r="H44" s="16" t="s">
         <v>150</v>
@@ -7232,17 +7229,17 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="39" t="s">
+      <c r="A48" s="36" t="s">
         <v>833</v>
       </c>
-      <c r="B48" s="39"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="39"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="39"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
     </row>
     <row r="49" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
@@ -7383,17 +7380,17 @@
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="39" t="s">
+      <c r="A55" s="36" t="s">
         <v>498</v>
       </c>
-      <c r="B55" s="39"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
     </row>
     <row r="56" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
@@ -7631,17 +7628,17 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="39" t="s">
+      <c r="A67" s="36" t="s">
         <v>504</v>
       </c>
-      <c r="B67" s="39"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="39"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="36"/>
+      <c r="H67" s="36"/>
+      <c r="I67" s="36"/>
     </row>
     <row r="68" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
@@ -7736,17 +7733,17 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="39" t="s">
+      <c r="A72" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="B72" s="39"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="39"/>
-      <c r="I72" s="39"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
     </row>
     <row r="73" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
@@ -7910,17 +7907,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="39" t="s">
+      <c r="A80" s="36" t="s">
         <v>512</v>
       </c>
-      <c r="B80" s="39"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
-      <c r="F80" s="39"/>
-      <c r="G80" s="39"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="39"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
@@ -8061,17 +8058,17 @@
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="39" t="s">
+      <c r="A87" s="36" t="s">
         <v>527</v>
       </c>
-      <c r="B87" s="39"/>
-      <c r="C87" s="39"/>
-      <c r="D87" s="39"/>
-      <c r="E87" s="39"/>
-      <c r="F87" s="39"/>
-      <c r="G87" s="39"/>
-      <c r="H87" s="39"/>
-      <c r="I87" s="39"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
     </row>
     <row r="88" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
@@ -8189,24 +8186,24 @@
       </c>
     </row>
     <row r="93" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="39" t="s">
+      <c r="A93" s="36" t="s">
         <v>542</v>
       </c>
-      <c r="B93" s="39"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="39"/>
-      <c r="F93" s="39"/>
-      <c r="G93" s="39"/>
-      <c r="H93" s="39"/>
-      <c r="I93" s="39"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
     </row>
     <row r="94" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
         <v>608</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>893</v>
+        <v>872</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -8215,13 +8212,13 @@
         <v>543</v>
       </c>
       <c r="G94" s="16" t="s">
-        <v>898</v>
+        <v>877</v>
       </c>
       <c r="H94" s="16" t="s">
         <v>544</v>
       </c>
       <c r="I94" s="16" t="s">
-        <v>886</v>
+        <v>865</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -8307,7 +8304,7 @@
         <v>551</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="H98" s="16" t="s">
         <v>552</v>
@@ -8330,7 +8327,7 @@
         <v>551</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="H99" s="16" t="s">
         <v>554</v>
@@ -8353,7 +8350,7 @@
         <v>551</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="H100" s="16" t="s">
         <v>556</v>
@@ -8364,39 +8361,39 @@
     </row>
     <row r="101" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
-        <v>894</v>
+        <v>873</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="14"/>
       <c r="E101" s="15"/>
       <c r="F101" s="14" t="s">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="H101" s="16" t="s">
         <v>544</v>
       </c>
       <c r="I101" s="16" t="s">
-        <v>886</v>
+        <v>865</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="40" t="s">
-        <v>885</v>
-      </c>
-      <c r="B102" s="39"/>
-      <c r="C102" s="39"/>
-      <c r="D102" s="39"/>
-      <c r="E102" s="39"/>
-      <c r="F102" s="39"/>
-      <c r="G102" s="39"/>
-      <c r="H102" s="39"/>
-      <c r="I102" s="39"/>
+      <c r="A102" s="42" t="s">
+        <v>864</v>
+      </c>
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+      <c r="G102" s="36"/>
+      <c r="H102" s="36"/>
+      <c r="I102" s="36"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
@@ -8518,20 +8515,20 @@
         <v>620</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
       <c r="E108" s="15"/>
       <c r="F108" s="14" t="s">
-        <v>888</v>
+        <v>867</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>889</v>
+        <v>868</v>
       </c>
       <c r="H108" s="16"/>
       <c r="I108" s="16" t="s">
-        <v>891</v>
+        <v>870</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
@@ -8559,10 +8556,10 @@
     </row>
     <row r="110" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
-        <v>900</v>
+        <v>879</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>905</v>
+        <v>884</v>
       </c>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -8577,15 +8574,15 @@
         <v>573</v>
       </c>
       <c r="I110" s="16" t="s">
-        <v>901</v>
+        <v>880</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
-        <v>902</v>
+        <v>881</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>903</v>
+        <v>882</v>
       </c>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -8600,15 +8597,15 @@
         <v>573</v>
       </c>
       <c r="I111" s="16" t="s">
-        <v>907</v>
+        <v>886</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
-        <v>904</v>
+        <v>883</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>906</v>
+        <v>885</v>
       </c>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -8623,7 +8620,7 @@
         <v>573</v>
       </c>
       <c r="I112" s="16" t="s">
-        <v>908</v>
+        <v>887</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -8720,7 +8717,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
-        <v>887</v>
+        <v>866</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>807</v>
@@ -8742,17 +8739,17 @@
       </c>
     </row>
     <row r="118" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="39" t="s">
+      <c r="A118" s="36" t="s">
         <v>585</v>
       </c>
-      <c r="B118" s="39"/>
-      <c r="C118" s="39"/>
-      <c r="D118" s="39"/>
-      <c r="E118" s="39"/>
-      <c r="F118" s="39"/>
-      <c r="G118" s="39"/>
-      <c r="H118" s="39"/>
-      <c r="I118" s="39"/>
+      <c r="B118" s="36"/>
+      <c r="C118" s="36"/>
+      <c r="D118" s="36"/>
+      <c r="E118" s="36"/>
+      <c r="F118" s="36"/>
+      <c r="G118" s="36"/>
+      <c r="H118" s="36"/>
+      <c r="I118" s="36"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
@@ -8847,17 +8844,17 @@
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="39" t="s">
+      <c r="A123" s="36" t="s">
         <v>599</v>
       </c>
-      <c r="B123" s="39"/>
-      <c r="C123" s="39"/>
-      <c r="D123" s="39"/>
-      <c r="E123" s="39"/>
-      <c r="F123" s="39"/>
-      <c r="G123" s="39"/>
-      <c r="H123" s="39"/>
-      <c r="I123" s="39"/>
+      <c r="B123" s="36"/>
+      <c r="C123" s="36"/>
+      <c r="D123" s="36"/>
+      <c r="E123" s="36"/>
+      <c r="F123" s="36"/>
+      <c r="G123" s="36"/>
+      <c r="H123" s="36"/>
+      <c r="I123" s="36"/>
     </row>
     <row r="124" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
@@ -8953,10 +8950,10 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
-        <v>910</v>
+        <v>889</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>911</v>
+        <v>890</v>
       </c>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -8967,11 +8964,9 @@
       <c r="I128" s="29"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="25" t="s">
-        <v>912</v>
-      </c>
+      <c r="A129" s="25"/>
       <c r="B129" s="26" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C129" s="26"/>
       <c r="D129" s="26"/>
@@ -8982,217 +8977,237 @@
       <c r="I129" s="29"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="41" t="s">
+      <c r="A130" s="25" t="s">
+        <v>891</v>
+      </c>
+      <c r="B130" s="26" t="s">
+        <v>892</v>
+      </c>
+      <c r="C130" s="26"/>
+      <c r="D130" s="26"/>
+      <c r="E130" s="27"/>
+      <c r="F130" s="26"/>
+      <c r="G130" s="28"/>
+      <c r="H130" s="28"/>
+      <c r="I130" s="29"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="43" t="s">
         <v>841</v>
       </c>
-      <c r="B130" s="42"/>
-      <c r="C130" s="42"/>
-      <c r="D130" s="42"/>
-      <c r="E130" s="42"/>
-      <c r="F130" s="42"/>
-      <c r="G130" s="42"/>
-      <c r="H130" s="42"/>
-      <c r="I130" s="43"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="17" t="s">
-        <v>842</v>
-      </c>
-      <c r="B131" s="24" t="s">
-        <v>909</v>
-      </c>
+      <c r="B131" s="44"/>
+      <c r="C131" s="44"/>
+      <c r="D131" s="44"/>
+      <c r="E131" s="44"/>
+      <c r="F131" s="44"/>
+      <c r="G131" s="44"/>
+      <c r="H131" s="44"/>
+      <c r="I131" s="45"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B132" s="24" t="s">
-        <v>856</v>
+        <v>888</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B133" s="24" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B134" s="24" t="s">
-        <v>858</v>
+        <v>894</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B135" s="24" t="s">
-        <v>859</v>
+        <v>895</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B136" s="24" t="s">
-        <v>860</v>
+        <v>898</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B137" s="24" t="s">
-        <v>861</v>
+        <v>896</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B138" s="24" t="s">
-        <v>862</v>
+        <v>904</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B139" s="24" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="17" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B140" s="24" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="17" t="s">
-        <v>852</v>
-      </c>
       <c r="B141" s="24" t="s">
-        <v>865</v>
+        <v>906</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="17" t="s">
-        <v>853</v>
-      </c>
       <c r="B142" s="24" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="17" t="s">
+      <c r="A143" s="39" t="s">
         <v>854</v>
       </c>
-      <c r="B143" s="24" t="s">
-        <v>867</v>
-      </c>
+      <c r="B143" s="40"/>
+      <c r="C143" s="40"/>
+      <c r="D143" s="40"/>
+      <c r="E143" s="40"/>
+      <c r="F143" s="40"/>
+      <c r="G143" s="40"/>
+      <c r="H143" s="40"/>
+      <c r="I143" s="41"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="17" t="s">
         <v>855</v>
       </c>
       <c r="B144" s="24" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="35" t="s">
-        <v>869</v>
-      </c>
-      <c r="B145" s="36"/>
-      <c r="C145" s="36"/>
-      <c r="D145" s="36"/>
-      <c r="E145" s="36"/>
-      <c r="F145" s="36"/>
-      <c r="G145" s="36"/>
-      <c r="H145" s="36"/>
-      <c r="I145" s="37"/>
+      <c r="A145" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="B145" s="24" t="s">
+        <v>859</v>
+      </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="17" t="s">
-        <v>870</v>
-      </c>
       <c r="B146" s="24" t="s">
-        <v>874</v>
+        <v>903</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="B147" s="24" t="s">
-        <v>875</v>
+        <v>897</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="B148" s="24" t="s">
-        <v>876</v>
-      </c>
+      <c r="A148" s="39" t="s">
+        <v>860</v>
+      </c>
+      <c r="B148" s="40"/>
+      <c r="C148" s="40"/>
+      <c r="D148" s="40"/>
+      <c r="E148" s="40"/>
+      <c r="F148" s="40"/>
+      <c r="G148" s="40"/>
+      <c r="H148" s="40"/>
+      <c r="I148" s="41"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="B149" s="24" t="s">
-        <v>877</v>
+        <v>905</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="35" t="s">
-        <v>878</v>
-      </c>
-      <c r="B150" s="36"/>
-      <c r="C150" s="36"/>
-      <c r="D150" s="36"/>
-      <c r="E150" s="36"/>
-      <c r="F150" s="36"/>
-      <c r="G150" s="36"/>
-      <c r="H150" s="36"/>
-      <c r="I150" s="37"/>
+      <c r="A150" s="17" t="s">
+        <v>862</v>
+      </c>
+      <c r="B150" s="24" t="s">
+        <v>863</v>
+      </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="17" t="s">
-        <v>879</v>
-      </c>
-      <c r="B151" s="24" t="s">
-        <v>882</v>
+      <c r="B151" s="18" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="17" t="s">
-        <v>880</v>
-      </c>
-      <c r="B152" s="24" t="s">
-        <v>883</v>
+      <c r="B152" s="18" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="17" t="s">
-        <v>881</v>
-      </c>
-      <c r="B153" s="24" t="s">
-        <v>884</v>
+      <c r="B153" s="18" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B154" s="18" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B155" s="18" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="50" t="s">
+        <v>908</v>
+      </c>
+      <c r="B156" s="44"/>
+      <c r="C156" s="44"/>
+      <c r="D156" s="44"/>
+      <c r="E156" s="44"/>
+      <c r="F156" s="44"/>
+      <c r="G156" s="44"/>
+      <c r="H156" s="44"/>
+      <c r="I156" s="45"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B157" s="18" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B158" s="18" t="s">
+        <v>910</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A28:I28"/>
+  <mergeCells count="35">
+    <mergeCell ref="A156:I156"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
@@ -9206,24 +9221,27 @@
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="G17:G22"/>
-    <mergeCell ref="A145:I145"/>
-    <mergeCell ref="A150:I150"/>
+    <mergeCell ref="A143:I143"/>
+    <mergeCell ref="A148:I148"/>
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="G42:G44"/>
     <mergeCell ref="A93:I93"/>
     <mergeCell ref="A102:I102"/>
     <mergeCell ref="A118:I118"/>
-    <mergeCell ref="A130:I130"/>
+    <mergeCell ref="A131:I131"/>
     <mergeCell ref="A55:I55"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A72:I72"/>
     <mergeCell ref="A80:I80"/>
     <mergeCell ref="A87:I87"/>
+    <mergeCell ref="A48:I48"/>
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="A123:I123"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="G17:G22"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A28:I28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
